--- a/OfficeIMO.TestAssets/Documents/ExcelPivotCorpus/AllErrorRanking/bottom-full-3.xlsx
+++ b/OfficeIMO.TestAssets/Documents/ExcelPivotCorpus/AllErrorRanking/bottom-full-3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\przemyslaw.klys.EVOTEC\.codex\worktrees\excel-csv-quality\OfficeIMO\OfficeIMO.TestAssets\Documents\ExcelPivotCorpus\AllErrorRanking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A3A9578B-F6DF-4157-83D6-45710D2FD869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7619D274-FCCB-417F-AA27-11787370E08F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="16170" windowWidth="28996" windowHeight="15675" xr2:uid="{CEF733BA-D080-4492-AFE6-44BB3944BE26}"/>
+    <workbookView xWindow="-98" yWindow="16170" windowWidth="28996" windowHeight="15675" xr2:uid="{F3A91D0F-5397-41DE-B064-00C49814C415}"/>
   </bookViews>
   <sheets>
     <sheet name="Grouped" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="127" r:id="rId3"/>
+    <pivotCache cacheId="159" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -134,7 +134,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46293.576892013887" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="7" xr:uid="{0BD1B27B-697D-4033-8FAC-B273FDE9ECAF}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46293.579463541668" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="7" xr:uid="{531F57E8-AEAA-4148-8D93-C7F137E26947}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:B8" sheet="Source"/>
   </cacheSource>
@@ -196,7 +196,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1C29E51F-A3D8-49A8-8FA9-29192CBE14F0}" name="AllErrorPivot" cacheId="127" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{27346121-1E45-42DB-80BC-086585F49637}" name="AllErrorPivot" cacheId="159" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A4:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="2">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" measureFilter="1">
@@ -573,7 +573,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67C59380-9C35-4D51-B4DC-C5039B04905C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB9BCEA8-176C-49D9-99BD-C134D5B26597}">
   <dimension ref="A4:B8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -627,7 +627,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22EB7057-86A5-413D-B69B-477E5BAD0213}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{684CDC6B-597F-40A6-9818-DC6450E5DD46}">
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
